--- a/EPTS Test Cases/1. General Login_Test_Cases.xlsx
+++ b/EPTS Test Cases/1. General Login_Test_Cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srinivas\Desktop\MogoMantra Project\EPTS\Test Cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srinivas\Desktop\MogoMantra Project\EPTS Testing\EPTS Test Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA4F42A-356E-4C63-81AF-C38F0A12843E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2E061F-6AB8-467D-9ECD-0CC6E0AFF845}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login Test Cases" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="125">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -358,9 +358,6 @@
     <t>Sl.No</t>
   </si>
   <si>
-    <t>Verify navigation is not trapped while tabbing</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Verify navigation between Username, Password, and Login button using </t>
     </r>
@@ -537,14 +534,30 @@
     </r>
   </si>
   <si>
-    <t>Verify navigation to Forgot Password using keyboard</t>
-  </si>
-  <si>
-    <t>Forgot Password page opens successfully.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Press </t>
+    <t>SC006</t>
+  </si>
+  <si>
+    <t>SC005</t>
+  </si>
+  <si>
+    <t>TC017</t>
+  </si>
+  <si>
+    <t>TC018</t>
+  </si>
+  <si>
+    <t>TC019</t>
+  </si>
+  <si>
+    <t>TC020</t>
+  </si>
+  <si>
+    <t>Keyboard navigation check</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Place cursor in username field.
+2. Press </t>
     </r>
     <r>
       <rPr>
@@ -562,77 +575,42 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> repeatedly across all elements.</t>
-    </r>
-  </si>
-  <si>
-    <t>Focus cycles smoothly or stops logically at the end.</t>
-  </si>
-  <si>
-    <t>SC006</t>
-  </si>
-  <si>
-    <t>SC005</t>
-  </si>
-  <si>
-    <t>TC017</t>
-  </si>
-  <si>
-    <t>TC018</t>
-  </si>
-  <si>
-    <t>TC019</t>
-  </si>
-  <si>
-    <t>TC020</t>
-  </si>
-  <si>
-    <t>TC022</t>
-  </si>
-  <si>
-    <t>TC023</t>
-  </si>
-  <si>
-    <t>Keyboard navigation check</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Place cursor in username field.
-2. Press </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Tab</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve"> key repeatedly.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Focus on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> key repeatedly.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Focus on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>Login button</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Login button</t>
+      <t xml:space="preserve">.
+2. Press </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Shift + Tab</t>
     </r>
     <r>
       <rPr>
@@ -642,7 +620,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.
+      <t xml:space="preserve"> repeatedly.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter valid username and password.
 2. Press </t>
     </r>
     <r>
@@ -651,7 +634,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>Shift + Tab</t>
+      <t>Tab</t>
     </r>
     <r>
       <rPr>
@@ -661,13 +644,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> repeatedly.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Enter valid username and password.
-2. Press </t>
+      <t xml:space="preserve"> to focus on Login button.
+3. Press </t>
     </r>
     <r>
       <rPr>
@@ -675,7 +653,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>Tab</t>
+      <t>Enter</t>
     </r>
     <r>
       <rPr>
@@ -685,67 +663,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> to focus on Login button.
-3. Press </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Enter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Use </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Tab</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to focus on "Forgot Password".
-2. Press </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Enter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>.</t>
     </r>
   </si>
@@ -768,14 +685,29 @@
     <t>Verify login with valid Admin credentials</t>
   </si>
   <si>
-    <t>TC024</t>
+    <t>Focus moved as per the flow</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>User navigates successfully by clicking enter</t>
+  </si>
+  <si>
+    <t>Visible</t>
+  </si>
+  <si>
+    <t>TC021</t>
+  </si>
+  <si>
+    <t>May be Error message should be professional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1227,8 +1159,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A2:L31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
@@ -1242,7 +1174,7 @@
     <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="34.5" customHeight="1">
+    <row r="2" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="7" t="s">
         <v>87</v>
       </c>
@@ -1250,7 +1182,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="34.5" customHeight="1">
+    <row r="3" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="7" t="s">
         <v>89</v>
       </c>
@@ -1258,25 +1190,25 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="34.5" customHeight="1">
+    <row r="4" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="7" t="s">
         <v>90</v>
       </c>
       <c r="D4" s="8"/>
     </row>
-    <row r="5" spans="1:11" ht="34.5" customHeight="1">
+    <row r="5" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
         <v>91</v>
       </c>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="1:11" ht="34.5" customHeight="1">
+    <row r="6" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="7" t="s">
         <v>92</v>
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>94</v>
       </c>
@@ -1311,7 +1243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60">
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -1340,7 +1272,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" ht="75">
+    <row r="12" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -1369,7 +1301,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" ht="60">
+    <row r="13" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -1398,7 +1330,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" ht="60">
+    <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -1427,7 +1359,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" ht="60">
+    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -1456,7 +1388,7 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
     </row>
-    <row r="16" spans="1:11" ht="60">
+    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -1485,7 +1417,7 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="60">
+    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -1514,7 +1446,7 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:11" ht="60">
+    <row r="18" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -1543,7 +1475,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:11" ht="60">
+    <row r="19" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -1571,8 +1503,11 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" ht="60">
+      <c r="L19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -1601,7 +1536,7 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
     </row>
-    <row r="21" spans="1:11" ht="75">
+    <row r="21" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -1630,7 +1565,7 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="60">
+    <row r="22" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -1659,7 +1594,7 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="60">
+    <row r="23" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -1688,7 +1623,7 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" ht="45">
+    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -1717,7 +1652,7 @@
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="45">
+    <row r="25" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -1746,7 +1681,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
     </row>
-    <row r="26" spans="1:11" ht="45">
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>16</v>
       </c>
@@ -1775,204 +1710,162 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30">
+    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>17</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="D27" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="G27" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
+      <c r="I27" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>120</v>
+      </c>
       <c r="K27" s="11"/>
     </row>
-    <row r="28" spans="1:11" ht="30">
+    <row r="28" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>18</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="D28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="G28" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="I28" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
+      <c r="J28" s="11" t="s">
+        <v>120</v>
+      </c>
       <c r="K28" s="11"/>
     </row>
-    <row r="29" spans="1:11" ht="45">
+    <row r="29" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>19</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="D29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>120</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>63</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
+        <v>100</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>120</v>
+      </c>
       <c r="K29" s="11"/>
     </row>
-    <row r="30" spans="1:11" ht="30">
+    <row r="30" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>20</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="K30" s="11"/>
+    </row>
+    <row r="31" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <v>23</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-    </row>
-    <row r="31" spans="1:11" ht="30">
-      <c r="A31" s="3">
-        <v>21</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-    </row>
-    <row r="32" spans="1:11" ht="30">
-      <c r="A32" s="3">
-        <v>22</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-    </row>
-    <row r="33" spans="1:8" ht="60">
-      <c r="A33" s="14">
-        <v>23</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
